--- a/artfynd/A 8038-2025 artfynd.xlsx
+++ b/artfynd/A 8038-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122904399</v>
+        <v>122904388</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370392</v>
+        <v>370196</v>
       </c>
       <c r="R2" t="n">
-        <v>6618282</v>
+        <v>6618342</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122904388</v>
+        <v>122904399</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,37 +809,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370196</v>
+        <v>370392</v>
       </c>
       <c r="R3" t="n">
-        <v>6618342</v>
+        <v>6618282</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 8038-2025 artfynd.xlsx
+++ b/artfynd/A 8038-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122904388</v>
+        <v>122904399</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -731,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370196</v>
+        <v>370392</v>
       </c>
       <c r="R2" t="n">
-        <v>6618342</v>
+        <v>6618282</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -793,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122904399</v>
+        <v>122904388</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,33 +805,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370392</v>
+        <v>370196</v>
       </c>
       <c r="R3" t="n">
-        <v>6618282</v>
+        <v>6618342</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 8038-2025 artfynd.xlsx
+++ b/artfynd/A 8038-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122904399</v>
+        <v>122904388</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370392</v>
+        <v>370196</v>
       </c>
       <c r="R2" t="n">
-        <v>6618282</v>
+        <v>6618342</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122904388</v>
+        <v>122904399</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,37 +809,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370196</v>
+        <v>370392</v>
       </c>
       <c r="R3" t="n">
-        <v>6618342</v>
+        <v>6618282</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 8038-2025 artfynd.xlsx
+++ b/artfynd/A 8038-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122904388</v>
+        <v>122904399</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -731,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370196</v>
+        <v>370392</v>
       </c>
       <c r="R2" t="n">
-        <v>6618342</v>
+        <v>6618282</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -793,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122904399</v>
+        <v>122904388</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,33 +805,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370392</v>
+        <v>370196</v>
       </c>
       <c r="R3" t="n">
-        <v>6618282</v>
+        <v>6618342</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
